--- a/media/Levels/Tutorial.xlsx
+++ b/media/Levels/Tutorial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C898CFA-1086-4FA7-88D3-D436E74E0BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFE636D-A73D-412C-A2D4-6720CB51E4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A669E15A-D514-4143-B895-055D763399A4}"/>
   </bookViews>
@@ -977,7 +977,7 @@
         <v>9</v>
       </c>
       <c r="U3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3">
         <v>9</v>
@@ -1437,7 +1437,7 @@
         <v>9</v>
       </c>
       <c r="W5" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
       <c r="X6" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1897,7 +1897,7 @@
         <v>9</v>
       </c>
       <c r="Y7" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z7">
         <v>9</v>
@@ -2357,7 +2357,7 @@
         <v>9</v>
       </c>
       <c r="AA9" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB9">
         <v>9</v>
@@ -4630,7 +4630,7 @@
         <v>9</v>
       </c>
       <c r="AB19" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC19">
         <v>9</v>
@@ -4857,7 +4857,7 @@
         <v>9</v>
       </c>
       <c r="AB20" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC20">
         <v>9</v>
@@ -5084,7 +5084,7 @@
         <v>9</v>
       </c>
       <c r="AB21" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -5992,7 +5992,7 @@
         <v>9</v>
       </c>
       <c r="AB25" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC25">
         <v>9</v>
@@ -6209,20 +6209,20 @@
       <c r="X26">
         <v>9</v>
       </c>
-      <c r="Y26" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="2">
-        <v>0</v>
+      <c r="Y26">
+        <v>9</v>
+      </c>
+      <c r="Z26">
+        <v>9</v>
+      </c>
+      <c r="AA26">
+        <v>9</v>
+      </c>
+      <c r="AB26" s="4">
+        <v>3</v>
+      </c>
+      <c r="AC26">
+        <v>9</v>
       </c>
       <c r="AD26">
         <v>9</v>
@@ -6670,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="AA28" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB28" s="2">
         <v>0</v>
@@ -6897,7 +6897,7 @@
         <v>0</v>
       </c>
       <c r="AA29" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB29" s="2">
         <v>0</v>
@@ -7344,20 +7344,20 @@
       <c r="X31">
         <v>9</v>
       </c>
-      <c r="Y31">
-        <v>9</v>
-      </c>
-      <c r="Z31">
-        <v>9</v>
-      </c>
-      <c r="AA31">
-        <v>9</v>
-      </c>
-      <c r="AB31" s="4">
-        <v>5</v>
-      </c>
-      <c r="AC31">
-        <v>9</v>
+      <c r="Y31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="2">
+        <v>0</v>
       </c>
       <c r="AD31">
         <v>9</v>
@@ -7578,7 +7578,7 @@
         <v>9</v>
       </c>
       <c r="AA32" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB32">
         <v>9</v>
@@ -7799,7 +7799,7 @@
         <v>9</v>
       </c>
       <c r="Z33" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA33">
         <v>9</v>
@@ -8247,7 +8247,7 @@
         <v>9</v>
       </c>
       <c r="X35" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y35">
         <v>9</v>
@@ -8695,7 +8695,7 @@
         <v>9</v>
       </c>
       <c r="V37" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -8919,7 +8919,7 @@
         <v>9</v>
       </c>
       <c r="U38" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V38">
         <v>9</v>
@@ -9143,7 +9143,7 @@
         <v>9</v>
       </c>
       <c r="T39" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U39">
         <v>9</v>
@@ -9591,7 +9591,7 @@
         <v>9</v>
       </c>
       <c r="R41" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S41">
         <v>9</v>

--- a/media/Levels/Tutorial.xlsx
+++ b/media/Levels/Tutorial.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFE636D-A73D-412C-A2D4-6720CB51E4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5F6321-8BF4-4D1D-8E30-CE8589735717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A669E15A-D514-4143-B895-055D763399A4}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{A669E15A-D514-4143-B895-055D763399A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3103,65 +3103,65 @@
       <c r="AV12">
         <v>9</v>
       </c>
-      <c r="AW12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BB12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BN12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BO12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BP12" s="3">
-        <v>0</v>
+      <c r="AW12">
+        <v>9</v>
+      </c>
+      <c r="AX12">
+        <v>9</v>
+      </c>
+      <c r="AY12">
+        <v>9</v>
+      </c>
+      <c r="AZ12">
+        <v>9</v>
+      </c>
+      <c r="BA12">
+        <v>9</v>
+      </c>
+      <c r="BB12">
+        <v>9</v>
+      </c>
+      <c r="BC12">
+        <v>9</v>
+      </c>
+      <c r="BD12">
+        <v>9</v>
+      </c>
+      <c r="BE12">
+        <v>9</v>
+      </c>
+      <c r="BF12">
+        <v>9</v>
+      </c>
+      <c r="BG12">
+        <v>9</v>
+      </c>
+      <c r="BH12">
+        <v>9</v>
+      </c>
+      <c r="BI12">
+        <v>9</v>
+      </c>
+      <c r="BJ12">
+        <v>9</v>
+      </c>
+      <c r="BK12">
+        <v>9</v>
+      </c>
+      <c r="BL12">
+        <v>9</v>
+      </c>
+      <c r="BM12">
+        <v>9</v>
+      </c>
+      <c r="BN12">
+        <v>9</v>
+      </c>
+      <c r="BO12">
+        <v>9</v>
+      </c>
+      <c r="BP12">
+        <v>9</v>
       </c>
       <c r="BQ12">
         <v>9</v>
@@ -5177,7 +5177,7 @@
         <v>0</v>
       </c>
       <c r="BG21" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BH21" s="3">
         <v>0</v>
@@ -5404,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="BG22" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH22" s="3">
         <v>0</v>
@@ -7643,65 +7643,65 @@
       <c r="AV32">
         <v>9</v>
       </c>
-      <c r="AW32">
-        <v>9</v>
-      </c>
-      <c r="AX32">
-        <v>9</v>
-      </c>
-      <c r="AY32">
-        <v>9</v>
-      </c>
-      <c r="AZ32">
-        <v>9</v>
-      </c>
-      <c r="BA32">
-        <v>9</v>
-      </c>
-      <c r="BB32">
-        <v>9</v>
-      </c>
-      <c r="BC32">
-        <v>9</v>
-      </c>
-      <c r="BD32">
-        <v>9</v>
-      </c>
-      <c r="BE32">
-        <v>9</v>
-      </c>
-      <c r="BF32">
-        <v>9</v>
-      </c>
-      <c r="BG32">
-        <v>9</v>
-      </c>
-      <c r="BH32">
-        <v>9</v>
-      </c>
-      <c r="BI32">
-        <v>9</v>
-      </c>
-      <c r="BJ32">
-        <v>9</v>
-      </c>
-      <c r="BK32">
-        <v>9</v>
-      </c>
-      <c r="BL32">
-        <v>9</v>
-      </c>
-      <c r="BM32">
-        <v>9</v>
-      </c>
-      <c r="BN32">
-        <v>9</v>
-      </c>
-      <c r="BO32">
-        <v>9</v>
-      </c>
-      <c r="BP32">
-        <v>9</v>
+      <c r="AW32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BM32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BO32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BP32" s="3">
+        <v>0</v>
       </c>
       <c r="BQ32">
         <v>9</v>
@@ -8073,20 +8073,20 @@
       <c r="AO34">
         <v>9</v>
       </c>
-      <c r="AP34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT34" s="2">
-        <v>0</v>
+      <c r="AP34">
+        <v>9</v>
+      </c>
+      <c r="AQ34">
+        <v>9</v>
+      </c>
+      <c r="AR34">
+        <v>9</v>
+      </c>
+      <c r="AS34">
+        <v>9</v>
+      </c>
+      <c r="AT34">
+        <v>9</v>
       </c>
       <c r="AU34">
         <v>9</v>
@@ -8300,20 +8300,20 @@
       <c r="AO35">
         <v>9</v>
       </c>
-      <c r="AP35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT35" s="2">
-        <v>0</v>
+      <c r="AP35">
+        <v>9</v>
+      </c>
+      <c r="AQ35">
+        <v>9</v>
+      </c>
+      <c r="AR35">
+        <v>9</v>
+      </c>
+      <c r="AS35">
+        <v>9</v>
+      </c>
+      <c r="AT35">
+        <v>9</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8527,20 +8527,20 @@
       <c r="AO36">
         <v>9</v>
       </c>
-      <c r="AP36" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ36" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR36" s="2">
-        <v>6</v>
-      </c>
-      <c r="AS36" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT36" s="2">
-        <v>0</v>
+      <c r="AP36">
+        <v>9</v>
+      </c>
+      <c r="AQ36">
+        <v>9</v>
+      </c>
+      <c r="AR36">
+        <v>9</v>
+      </c>
+      <c r="AS36">
+        <v>9</v>
+      </c>
+      <c r="AT36">
+        <v>9</v>
       </c>
       <c r="AU36">
         <v>9</v>
@@ -8754,20 +8754,20 @@
       <c r="AO37">
         <v>9</v>
       </c>
-      <c r="AP37" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ37" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR37" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS37" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT37" s="2">
-        <v>0</v>
+      <c r="AP37">
+        <v>9</v>
+      </c>
+      <c r="AQ37">
+        <v>9</v>
+      </c>
+      <c r="AR37">
+        <v>9</v>
+      </c>
+      <c r="AS37">
+        <v>9</v>
+      </c>
+      <c r="AT37">
+        <v>9</v>
       </c>
       <c r="AU37">
         <v>9</v>
@@ -8981,20 +8981,20 @@
       <c r="AO38">
         <v>9</v>
       </c>
-      <c r="AP38" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ38" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR38" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS38" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT38" s="2">
-        <v>0</v>
+      <c r="AP38">
+        <v>9</v>
+      </c>
+      <c r="AQ38">
+        <v>9</v>
+      </c>
+      <c r="AR38">
+        <v>9</v>
+      </c>
+      <c r="AS38">
+        <v>9</v>
+      </c>
+      <c r="AT38">
+        <v>9</v>
       </c>
       <c r="AU38">
         <v>9</v>
@@ -9716,20 +9716,20 @@
       <c r="BG41">
         <v>9</v>
       </c>
-      <c r="BH41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL41" s="2">
-        <v>0</v>
+      <c r="BH41">
+        <v>9</v>
+      </c>
+      <c r="BI41">
+        <v>9</v>
+      </c>
+      <c r="BJ41">
+        <v>9</v>
+      </c>
+      <c r="BK41">
+        <v>9</v>
+      </c>
+      <c r="BL41">
+        <v>9</v>
       </c>
       <c r="BM41">
         <v>9</v>
@@ -9943,20 +9943,20 @@
       <c r="BG42">
         <v>9</v>
       </c>
-      <c r="BH42" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI42" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ42" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK42" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL42" s="2">
-        <v>0</v>
+      <c r="BH42">
+        <v>9</v>
+      </c>
+      <c r="BI42">
+        <v>9</v>
+      </c>
+      <c r="BJ42">
+        <v>9</v>
+      </c>
+      <c r="BK42">
+        <v>9</v>
+      </c>
+      <c r="BL42">
+        <v>9</v>
       </c>
       <c r="BM42">
         <v>9</v>
@@ -10170,20 +10170,20 @@
       <c r="BG43">
         <v>9</v>
       </c>
-      <c r="BH43" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI43" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ43" s="2">
-        <v>6</v>
-      </c>
-      <c r="BK43" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL43" s="2">
-        <v>0</v>
+      <c r="BH43">
+        <v>9</v>
+      </c>
+      <c r="BI43">
+        <v>9</v>
+      </c>
+      <c r="BJ43">
+        <v>9</v>
+      </c>
+      <c r="BK43">
+        <v>9</v>
+      </c>
+      <c r="BL43">
+        <v>9</v>
       </c>
       <c r="BM43">
         <v>9</v>
@@ -10397,20 +10397,20 @@
       <c r="BG44">
         <v>9</v>
       </c>
-      <c r="BH44" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI44" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ44" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK44" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL44" s="2">
-        <v>0</v>
+      <c r="BH44">
+        <v>9</v>
+      </c>
+      <c r="BI44">
+        <v>9</v>
+      </c>
+      <c r="BJ44">
+        <v>9</v>
+      </c>
+      <c r="BK44">
+        <v>9</v>
+      </c>
+      <c r="BL44">
+        <v>9</v>
       </c>
       <c r="BM44">
         <v>9</v>
@@ -10624,20 +10624,20 @@
       <c r="BG45">
         <v>9</v>
       </c>
-      <c r="BH45" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI45" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ45" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK45" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL45" s="2">
-        <v>0</v>
+      <c r="BH45">
+        <v>9</v>
+      </c>
+      <c r="BI45">
+        <v>9</v>
+      </c>
+      <c r="BJ45">
+        <v>9</v>
+      </c>
+      <c r="BK45">
+        <v>9</v>
+      </c>
+      <c r="BL45">
+        <v>9</v>
       </c>
       <c r="BM45">
         <v>9</v>
@@ -12652,20 +12652,20 @@
       <c r="BB54">
         <v>9</v>
       </c>
-      <c r="BC54">
-        <v>9</v>
-      </c>
-      <c r="BD54">
-        <v>9</v>
-      </c>
-      <c r="BE54">
-        <v>9</v>
-      </c>
-      <c r="BF54">
-        <v>9</v>
-      </c>
-      <c r="BG54">
-        <v>9</v>
+      <c r="BC54" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD54" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE54" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF54" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG54" s="2">
+        <v>0</v>
       </c>
       <c r="BH54">
         <v>9</v>
@@ -12879,20 +12879,20 @@
       <c r="BB55">
         <v>9</v>
       </c>
-      <c r="BC55">
-        <v>9</v>
-      </c>
-      <c r="BD55">
-        <v>9</v>
-      </c>
-      <c r="BE55">
-        <v>9</v>
-      </c>
-      <c r="BF55">
-        <v>9</v>
-      </c>
-      <c r="BG55">
-        <v>9</v>
+      <c r="BC55" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD55" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE55" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF55" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG55" s="2">
+        <v>0</v>
       </c>
       <c r="BH55">
         <v>9</v>
@@ -13106,20 +13106,20 @@
       <c r="BB56">
         <v>9</v>
       </c>
-      <c r="BC56">
-        <v>9</v>
-      </c>
-      <c r="BD56">
-        <v>9</v>
-      </c>
-      <c r="BE56">
-        <v>9</v>
-      </c>
-      <c r="BF56">
-        <v>9</v>
-      </c>
-      <c r="BG56">
-        <v>9</v>
+      <c r="BC56" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD56" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE56" s="2">
+        <v>6</v>
+      </c>
+      <c r="BF56" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG56" s="2">
+        <v>0</v>
       </c>
       <c r="BH56">
         <v>9</v>
@@ -13333,20 +13333,20 @@
       <c r="BB57">
         <v>9</v>
       </c>
-      <c r="BC57">
-        <v>9</v>
-      </c>
-      <c r="BD57">
-        <v>9</v>
-      </c>
-      <c r="BE57">
-        <v>9</v>
-      </c>
-      <c r="BF57">
-        <v>9</v>
-      </c>
-      <c r="BG57">
-        <v>9</v>
+      <c r="BC57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG57" s="2">
+        <v>0</v>
       </c>
       <c r="BH57">
         <v>9</v>
@@ -13560,20 +13560,20 @@
       <c r="BB58">
         <v>9</v>
       </c>
-      <c r="BC58">
-        <v>9</v>
-      </c>
-      <c r="BD58">
-        <v>9</v>
-      </c>
-      <c r="BE58">
-        <v>9</v>
-      </c>
-      <c r="BF58">
-        <v>9</v>
-      </c>
-      <c r="BG58">
-        <v>9</v>
+      <c r="BC58" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD58" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE58" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF58" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG58" s="2">
+        <v>0</v>
       </c>
       <c r="BH58">
         <v>9</v>
@@ -14244,20 +14244,20 @@
       <c r="BC61">
         <v>9</v>
       </c>
-      <c r="BD61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH61" s="2">
-        <v>0</v>
+      <c r="BD61">
+        <v>9</v>
+      </c>
+      <c r="BE61">
+        <v>9</v>
+      </c>
+      <c r="BF61">
+        <v>9</v>
+      </c>
+      <c r="BG61">
+        <v>9</v>
+      </c>
+      <c r="BH61">
+        <v>9</v>
       </c>
       <c r="BI61">
         <v>9</v>
@@ -14471,20 +14471,20 @@
       <c r="BC62">
         <v>9</v>
       </c>
-      <c r="BD62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH62" s="2">
-        <v>0</v>
+      <c r="BD62">
+        <v>9</v>
+      </c>
+      <c r="BE62">
+        <v>9</v>
+      </c>
+      <c r="BF62">
+        <v>9</v>
+      </c>
+      <c r="BG62">
+        <v>9</v>
+      </c>
+      <c r="BH62">
+        <v>9</v>
       </c>
       <c r="BI62">
         <v>9</v>
@@ -14698,20 +14698,20 @@
       <c r="BC63">
         <v>9</v>
       </c>
-      <c r="BD63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF63" s="2">
-        <v>6</v>
-      </c>
-      <c r="BG63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH63" s="2">
-        <v>0</v>
+      <c r="BD63">
+        <v>9</v>
+      </c>
+      <c r="BE63">
+        <v>9</v>
+      </c>
+      <c r="BF63">
+        <v>9</v>
+      </c>
+      <c r="BG63">
+        <v>9</v>
+      </c>
+      <c r="BH63">
+        <v>9</v>
       </c>
       <c r="BI63">
         <v>9</v>
@@ -14925,20 +14925,20 @@
       <c r="BC64">
         <v>9</v>
       </c>
-      <c r="BD64" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE64" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF64" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG64" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH64" s="2">
-        <v>0</v>
+      <c r="BD64">
+        <v>9</v>
+      </c>
+      <c r="BE64">
+        <v>9</v>
+      </c>
+      <c r="BF64">
+        <v>9</v>
+      </c>
+      <c r="BG64">
+        <v>9</v>
+      </c>
+      <c r="BH64">
+        <v>9</v>
       </c>
       <c r="BI64">
         <v>9</v>
@@ -15152,20 +15152,20 @@
       <c r="BC65">
         <v>9</v>
       </c>
-      <c r="BD65" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE65" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF65" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG65" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH65" s="2">
-        <v>0</v>
+      <c r="BD65">
+        <v>9</v>
+      </c>
+      <c r="BE65">
+        <v>9</v>
+      </c>
+      <c r="BF65">
+        <v>9</v>
+      </c>
+      <c r="BG65">
+        <v>9</v>
+      </c>
+      <c r="BH65">
+        <v>9</v>
       </c>
       <c r="BI65">
         <v>9</v>

--- a/media/Levels/Tutorial.xlsx
+++ b/media/Levels/Tutorial.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5F6321-8BF4-4D1D-8E30-CE8589735717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5299BD0-2D62-4688-9C44-FDC2ECB79DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{A669E15A-D514-4143-B895-055D763399A4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A669E15A-D514-4143-B895-055D763399A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,10 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -466,115 +470,115 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1" s="1">
+        <v>0</v>
+      </c>
+      <c r="J1" s="1">
+        <v>0</v>
+      </c>
+      <c r="K1" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1" s="1">
+        <v>0</v>
+      </c>
+      <c r="T1" s="1">
+        <v>0</v>
+      </c>
+      <c r="U1" s="1">
+        <v>0</v>
+      </c>
+      <c r="V1" s="1">
+        <v>0</v>
+      </c>
+      <c r="W1" s="1">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK1" s="1">
         <v>1</v>
       </c>
-      <c r="C1" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1">
-        <v>1</v>
-      </c>
-      <c r="I1" s="1">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>0</v>
-      </c>
-      <c r="M1" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1" s="1">
-        <v>1</v>
-      </c>
-      <c r="O1" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>1</v>
-      </c>
-      <c r="R1" s="1">
-        <v>0</v>
-      </c>
-      <c r="S1" s="1">
-        <v>0</v>
-      </c>
-      <c r="T1" s="1">
-        <v>1</v>
-      </c>
-      <c r="U1" s="1">
-        <v>0</v>
-      </c>
-      <c r="V1" s="1">
-        <v>0</v>
-      </c>
-      <c r="W1" s="1">
-        <v>1</v>
-      </c>
-      <c r="X1" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y1" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z1" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA1" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB1" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC1" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD1" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE1" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF1" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG1" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH1" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI1" s="1">
-        <v>1</v>
-      </c>
-      <c r="AJ1" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK1" s="1">
-        <v>0</v>
-      </c>
       <c r="AL1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM1" s="1">
         <v>0</v>
@@ -583,7 +587,7 @@
         <v>0</v>
       </c>
       <c r="AO1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP1" s="1">
         <v>0</v>
@@ -592,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="AR1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS1" s="1">
         <v>0</v>
@@ -601,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="AU1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV1" s="1">
         <v>0</v>
@@ -610,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="AX1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY1" s="1">
         <v>0</v>
@@ -619,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="BA1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB1" s="1">
         <v>0</v>
@@ -628,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="BD1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE1" s="1">
         <v>0</v>
@@ -637,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="BG1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH1" s="1">
         <v>0</v>
@@ -646,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="BJ1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK1" s="1">
         <v>0</v>
@@ -655,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="BM1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN1" s="1">
         <v>0</v>
@@ -664,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="BP1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ1" s="1">
         <v>0</v>
@@ -673,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="BS1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT1" s="1">
         <v>0</v>
@@ -682,7 +686,7 @@
         <v>0</v>
       </c>
       <c r="BV1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW1" s="1">
         <v>0</v>
@@ -690,7 +694,7 @@
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>9</v>
@@ -912,7 +916,7 @@
         <v>9</v>
       </c>
       <c r="BW2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:75" x14ac:dyDescent="0.45">
@@ -1144,7 +1148,7 @@
     </row>
     <row r="4" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -1366,7 +1370,7 @@
         <v>9</v>
       </c>
       <c r="BW4" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:75" x14ac:dyDescent="0.45">
@@ -1598,7 +1602,7 @@
     </row>
     <row r="6" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B6">
         <v>9</v>
@@ -1820,7 +1824,7 @@
         <v>9</v>
       </c>
       <c r="BW6" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:75" x14ac:dyDescent="0.45">
@@ -2052,7 +2056,7 @@
     </row>
     <row r="8" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -2274,7 +2278,7 @@
         <v>9</v>
       </c>
       <c r="BW8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:75" x14ac:dyDescent="0.45">
@@ -2506,7 +2510,7 @@
     </row>
     <row r="10" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -2728,7 +2732,7 @@
         <v>9</v>
       </c>
       <c r="BW10" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:75" x14ac:dyDescent="0.45">
@@ -2960,7 +2964,7 @@
     </row>
     <row r="12" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B12">
         <v>9</v>
@@ -3182,7 +3186,7 @@
         <v>9</v>
       </c>
       <c r="BW12" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:75" x14ac:dyDescent="0.45">
@@ -3414,7 +3418,7 @@
     </row>
     <row r="14" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B14">
         <v>9</v>
@@ -3636,7 +3640,7 @@
         <v>9</v>
       </c>
       <c r="BW14" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:75" x14ac:dyDescent="0.45">
@@ -3868,7 +3872,7 @@
     </row>
     <row r="16" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B16">
         <v>9</v>
@@ -4090,7 +4094,7 @@
         <v>9</v>
       </c>
       <c r="BW16" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:75" x14ac:dyDescent="0.45">
@@ -4322,7 +4326,7 @@
     </row>
     <row r="18" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B18">
         <v>9</v>
@@ -4544,7 +4548,7 @@
         <v>9</v>
       </c>
       <c r="BW18" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:75" x14ac:dyDescent="0.45">
@@ -4776,7 +4780,7 @@
     </row>
     <row r="20" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B20">
         <v>9</v>
@@ -4998,7 +5002,7 @@
         <v>9</v>
       </c>
       <c r="BW20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:75" x14ac:dyDescent="0.45">
@@ -5230,7 +5234,7 @@
     </row>
     <row r="22" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B22">
         <v>9</v>
@@ -5452,7 +5456,7 @@
         <v>9</v>
       </c>
       <c r="BW22" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:75" x14ac:dyDescent="0.45">
@@ -5684,7 +5688,7 @@
     </row>
     <row r="24" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B24">
         <v>9</v>
@@ -5906,7 +5910,7 @@
         <v>9</v>
       </c>
       <c r="BW24" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:75" x14ac:dyDescent="0.45">
@@ -6138,7 +6142,7 @@
     </row>
     <row r="26" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B26">
         <v>9</v>
@@ -6360,7 +6364,7 @@
         <v>9</v>
       </c>
       <c r="BW26" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:75" x14ac:dyDescent="0.45">
@@ -6592,7 +6596,7 @@
     </row>
     <row r="28" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B28">
         <v>9</v>
@@ -6814,7 +6818,7 @@
         <v>9</v>
       </c>
       <c r="BW28" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:75" x14ac:dyDescent="0.45">
@@ -7046,7 +7050,7 @@
     </row>
     <row r="30" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B30">
         <v>9</v>
@@ -7268,7 +7272,7 @@
         <v>9</v>
       </c>
       <c r="BW30" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:75" x14ac:dyDescent="0.45">
@@ -7500,7 +7504,7 @@
     </row>
     <row r="32" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B32">
         <v>9</v>
@@ -7722,7 +7726,7 @@
         <v>9</v>
       </c>
       <c r="BW32" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:75" x14ac:dyDescent="0.45">
@@ -7951,7 +7955,7 @@
     </row>
     <row r="34" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B34">
         <v>9</v>
@@ -8173,7 +8177,7 @@
         <v>9</v>
       </c>
       <c r="BW34" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:75" x14ac:dyDescent="0.45">
@@ -8405,7 +8409,7 @@
     </row>
     <row r="36" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B36">
         <v>9</v>
@@ -8627,7 +8631,7 @@
         <v>9</v>
       </c>
       <c r="BW36" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:75" x14ac:dyDescent="0.45">
@@ -8854,12 +8858,12 @@
         <v>9</v>
       </c>
       <c r="BW37" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B38">
         <v>9</v>
@@ -9081,12 +9085,12 @@
         <v>9</v>
       </c>
       <c r="BW38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B39">
         <v>9</v>
@@ -9313,7 +9317,7 @@
     </row>
     <row r="40" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B40">
         <v>9</v>
@@ -9535,7 +9539,7 @@
         <v>9</v>
       </c>
       <c r="BW40" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:75" x14ac:dyDescent="0.45">
@@ -9767,7 +9771,7 @@
     </row>
     <row r="42" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B42">
         <v>9</v>
@@ -9989,7 +9993,7 @@
         <v>9</v>
       </c>
       <c r="BW42" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:75" x14ac:dyDescent="0.45">
@@ -10221,7 +10225,7 @@
     </row>
     <row r="44" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -10443,7 +10447,7 @@
         <v>9</v>
       </c>
       <c r="BW44" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:75" x14ac:dyDescent="0.45">
@@ -10675,7 +10679,7 @@
     </row>
     <row r="46" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B46" s="3">
         <v>0</v>
@@ -10897,7 +10901,7 @@
         <v>9</v>
       </c>
       <c r="BW46" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:75" x14ac:dyDescent="0.45">
@@ -11129,7 +11133,7 @@
     </row>
     <row r="48" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B48" s="3">
         <v>0</v>
@@ -11351,7 +11355,7 @@
         <v>9</v>
       </c>
       <c r="BW48" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:75" x14ac:dyDescent="0.45">
@@ -11583,7 +11587,7 @@
     </row>
     <row r="50" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B50" s="3">
         <v>0</v>
@@ -11805,7 +11809,7 @@
         <v>9</v>
       </c>
       <c r="BW50" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:75" x14ac:dyDescent="0.45">
@@ -12037,7 +12041,7 @@
     </row>
     <row r="52" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A52" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B52" s="3">
         <v>0</v>
@@ -12259,7 +12263,7 @@
         <v>9</v>
       </c>
       <c r="BW52" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:75" x14ac:dyDescent="0.45">
@@ -12491,7 +12495,7 @@
     </row>
     <row r="54" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A54" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B54" s="3">
         <v>0</v>
@@ -12713,7 +12717,7 @@
         <v>9</v>
       </c>
       <c r="BW54" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:75" x14ac:dyDescent="0.45">
@@ -12945,7 +12949,7 @@
     </row>
     <row r="56" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B56" s="3">
         <v>0</v>
@@ -13167,7 +13171,7 @@
         <v>9</v>
       </c>
       <c r="BW56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:75" x14ac:dyDescent="0.45">
@@ -13399,7 +13403,7 @@
     </row>
     <row r="58" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B58" s="3">
         <v>0</v>
@@ -13621,7 +13625,7 @@
         <v>9</v>
       </c>
       <c r="BW58" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:75" x14ac:dyDescent="0.45">
@@ -13853,7 +13857,7 @@
     </row>
     <row r="60" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A60" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B60" s="3">
         <v>0</v>
@@ -14075,7 +14079,7 @@
         <v>9</v>
       </c>
       <c r="BW60" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:75" x14ac:dyDescent="0.45">
@@ -14307,7 +14311,7 @@
     </row>
     <row r="62" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B62" s="3">
         <v>0</v>
@@ -14529,7 +14533,7 @@
         <v>9</v>
       </c>
       <c r="BW62" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:75" x14ac:dyDescent="0.45">
@@ -14761,7 +14765,7 @@
     </row>
     <row r="64" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A64" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B64">
         <v>9</v>
@@ -14983,7 +14987,7 @@
         <v>9</v>
       </c>
       <c r="BW64" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:75" x14ac:dyDescent="0.45">
@@ -15215,7 +15219,7 @@
     </row>
     <row r="66" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A66" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B66">
         <v>9</v>
@@ -15437,7 +15441,7 @@
         <v>9</v>
       </c>
       <c r="BW66" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:75" x14ac:dyDescent="0.45">
@@ -15669,7 +15673,7 @@
     </row>
     <row r="68" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B68">
         <v>9</v>
@@ -15891,7 +15895,7 @@
         <v>9</v>
       </c>
       <c r="BW68" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:75" x14ac:dyDescent="0.45">
@@ -16123,7 +16127,7 @@
     </row>
     <row r="70" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B70">
         <v>9</v>
@@ -16345,7 +16349,7 @@
         <v>9</v>
       </c>
       <c r="BW70" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:75" x14ac:dyDescent="0.45">
@@ -16577,7 +16581,7 @@
     </row>
     <row r="72" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B72">
         <v>9</v>
@@ -16799,7 +16803,7 @@
         <v>9</v>
       </c>
       <c r="BW72" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:75" x14ac:dyDescent="0.45">
@@ -17031,7 +17035,7 @@
     </row>
     <row r="74" spans="1:75" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B74">
         <v>9</v>
@@ -17253,7 +17257,7 @@
         <v>9</v>
       </c>
       <c r="BW74" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:75" x14ac:dyDescent="0.45">
@@ -17261,124 +17265,124 @@
         <v>0</v>
       </c>
       <c r="B75" s="1">
+        <v>0</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
+      </c>
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+      <c r="I75" s="1">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1">
+        <v>0</v>
+      </c>
+      <c r="K75" s="1">
+        <v>0</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1">
+        <v>0</v>
+      </c>
+      <c r="N75" s="1">
+        <v>0</v>
+      </c>
+      <c r="O75" s="1">
+        <v>0</v>
+      </c>
+      <c r="P75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>0</v>
+      </c>
+      <c r="R75" s="1">
+        <v>0</v>
+      </c>
+      <c r="S75" s="1">
+        <v>0</v>
+      </c>
+      <c r="T75" s="1">
+        <v>0</v>
+      </c>
+      <c r="U75" s="1">
+        <v>0</v>
+      </c>
+      <c r="V75" s="1">
+        <v>0</v>
+      </c>
+      <c r="W75" s="1">
+        <v>0</v>
+      </c>
+      <c r="X75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="1">
         <v>1</v>
       </c>
-      <c r="C75" s="1">
-        <v>0</v>
-      </c>
-      <c r="D75" s="1">
-        <v>0</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="1">
-        <v>0</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0</v>
-      </c>
-      <c r="H75" s="1">
-        <v>1</v>
-      </c>
-      <c r="I75" s="1">
-        <v>0</v>
-      </c>
-      <c r="J75" s="1">
-        <v>0</v>
-      </c>
-      <c r="K75" s="1">
-        <v>0</v>
-      </c>
-      <c r="L75" s="1">
-        <v>1</v>
-      </c>
-      <c r="M75" s="1">
-        <v>0</v>
-      </c>
-      <c r="N75" s="1">
-        <v>1</v>
-      </c>
-      <c r="O75" s="1">
-        <v>0</v>
-      </c>
-      <c r="P75" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="1">
-        <v>1</v>
-      </c>
-      <c r="R75" s="1">
-        <v>0</v>
-      </c>
-      <c r="S75" s="1">
-        <v>0</v>
-      </c>
-      <c r="T75" s="1">
-        <v>1</v>
-      </c>
-      <c r="U75" s="1">
-        <v>0</v>
-      </c>
-      <c r="V75" s="1">
-        <v>0</v>
-      </c>
-      <c r="W75" s="1">
-        <v>1</v>
-      </c>
-      <c r="X75" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y75" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z75" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC75" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF75" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI75" s="1">
-        <v>1</v>
-      </c>
-      <c r="AJ75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL75" s="1">
-        <v>1</v>
-      </c>
-      <c r="AM75" s="1">
-        <v>0</v>
-      </c>
       <c r="AN75" s="1">
         <v>0</v>
       </c>
       <c r="AO75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP75" s="1">
         <v>0</v>
@@ -17387,7 +17391,7 @@
         <v>0</v>
       </c>
       <c r="AR75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS75" s="1">
         <v>0</v>
@@ -17396,7 +17400,7 @@
         <v>0</v>
       </c>
       <c r="AU75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV75" s="1">
         <v>0</v>
@@ -17405,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="AX75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY75" s="1">
         <v>0</v>
@@ -17414,7 +17418,7 @@
         <v>0</v>
       </c>
       <c r="BA75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB75" s="1">
         <v>0</v>
@@ -17423,7 +17427,7 @@
         <v>0</v>
       </c>
       <c r="BD75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE75" s="1">
         <v>0</v>
@@ -17432,7 +17436,7 @@
         <v>0</v>
       </c>
       <c r="BG75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH75" s="1">
         <v>0</v>
@@ -17441,7 +17445,7 @@
         <v>0</v>
       </c>
       <c r="BJ75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK75" s="1">
         <v>0</v>
@@ -17450,7 +17454,7 @@
         <v>0</v>
       </c>
       <c r="BM75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN75" s="1">
         <v>0</v>
@@ -17459,7 +17463,7 @@
         <v>0</v>
       </c>
       <c r="BP75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ75" s="1">
         <v>0</v>
@@ -17468,7 +17472,7 @@
         <v>0</v>
       </c>
       <c r="BS75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT75" s="1">
         <v>0</v>
@@ -17477,7 +17481,7 @@
         <v>0</v>
       </c>
       <c r="BV75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW75" s="1">
         <v>0</v>
